--- a/out/RQ3_tool_consistency_and_node_usage_consistency/RQ3_tool_consistency_and_node_usage_consistency.xlsx
+++ b/out/RQ3_tool_consistency_and_node_usage_consistency/RQ3_tool_consistency_and_node_usage_consistency.xlsx
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -14780,7 +14780,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -16678,7 +16678,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -17408,7 +17408,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -17481,7 +17481,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -17554,7 +17554,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -18065,7 +18065,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -19160,7 +19160,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -19379,7 +19379,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -19452,7 +19452,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -19671,7 +19671,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -20036,7 +20036,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -20109,7 +20109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -20182,7 +20182,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -20693,7 +20693,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -20766,7 +20766,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -21058,7 +21058,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -21204,7 +21204,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -21423,7 +21423,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -21496,7 +21496,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -21569,7 +21569,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -21788,7 +21788,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -21861,7 +21861,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -22007,7 +22007,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -22080,7 +22080,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -22518,7 +22518,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -22591,7 +22591,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -22664,7 +22664,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -23029,7 +23029,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -23321,7 +23321,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -23467,7 +23467,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -23540,7 +23540,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -23613,7 +23613,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -23686,7 +23686,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -23759,7 +23759,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -23832,7 +23832,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -23905,7 +23905,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -23978,7 +23978,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -24124,7 +24124,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -29010,7 +29010,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -29083,7 +29083,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -29156,7 +29156,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -29229,7 +29229,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -29375,7 +29375,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -29448,7 +29448,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -29521,7 +29521,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -29594,7 +29594,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -29667,7 +29667,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -29740,7 +29740,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -29813,7 +29813,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -29886,7 +29886,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -29959,7 +29959,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -30032,7 +30032,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -30105,7 +30105,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -30178,7 +30178,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -30251,7 +30251,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -30397,7 +30397,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -30543,7 +30543,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -30616,7 +30616,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -30689,7 +30689,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -30762,7 +30762,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -30835,7 +30835,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -30908,7 +30908,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -30981,7 +30981,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -31054,7 +31054,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -31127,7 +31127,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -31273,7 +31273,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -31492,7 +31492,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -31565,7 +31565,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -31711,7 +31711,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -31784,7 +31784,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -31857,7 +31857,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -31930,7 +31930,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -32003,7 +32003,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -32149,7 +32149,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -32222,7 +32222,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -32295,7 +32295,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -32368,7 +32368,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -32514,7 +32514,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -32587,7 +32587,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -32660,7 +32660,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -32733,7 +32733,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -32806,7 +32806,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -32952,7 +32952,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -33025,7 +33025,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -33098,7 +33098,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -33171,7 +33171,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -33317,7 +33317,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -33390,7 +33390,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -33463,7 +33463,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -33536,7 +33536,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -33609,7 +33609,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -33755,7 +33755,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -33901,7 +33901,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -34047,7 +34047,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -34120,7 +34120,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -34193,7 +34193,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -34266,7 +34266,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -34339,7 +34339,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -34412,7 +34412,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -34485,7 +34485,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -34558,7 +34558,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -34631,7 +34631,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -34704,7 +34704,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -34777,7 +34777,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -34850,7 +34850,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -34923,7 +34923,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -34996,7 +34996,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -35069,7 +35069,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -35142,7 +35142,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -35215,7 +35215,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -35288,7 +35288,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -35361,7 +35361,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -35507,7 +35507,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -35580,7 +35580,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -35653,7 +35653,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -35726,7 +35726,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -35799,7 +35799,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -35872,7 +35872,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -35945,7 +35945,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -36018,7 +36018,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -36091,7 +36091,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -36164,7 +36164,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -36237,7 +36237,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -36310,7 +36310,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -36383,7 +36383,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -36456,7 +36456,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -36529,7 +36529,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -36602,7 +36602,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -36675,7 +36675,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -36748,7 +36748,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -36821,7 +36821,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -36894,7 +36894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -36967,7 +36967,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -37113,7 +37113,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -37186,7 +37186,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -37259,7 +37259,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -37405,7 +37405,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -37478,7 +37478,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -37551,7 +37551,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -37624,7 +37624,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -37697,7 +37697,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -37770,7 +37770,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -37843,7 +37843,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -37916,7 +37916,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -37989,7 +37989,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -38062,7 +38062,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -38135,7 +38135,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -38208,7 +38208,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -38281,7 +38281,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -38354,7 +38354,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -38427,7 +38427,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -38500,7 +38500,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -38573,7 +38573,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -38646,7 +38646,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -38719,7 +38719,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -38792,7 +38792,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -38938,7 +38938,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -39011,7 +39011,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -39084,7 +39084,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -39157,7 +39157,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -39230,7 +39230,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -39303,7 +39303,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -39376,7 +39376,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -39449,7 +39449,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -39522,7 +39522,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -39595,7 +39595,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -39668,7 +39668,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -39741,7 +39741,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -39814,7 +39814,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -39887,7 +39887,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -39960,7 +39960,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -40033,7 +40033,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -40106,7 +40106,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -40179,7 +40179,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -40252,7 +40252,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -40398,7 +40398,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -40471,7 +40471,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -40544,7 +40544,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -40617,7 +40617,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -40690,7 +40690,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -40763,7 +40763,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -40836,7 +40836,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -40909,7 +40909,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -40982,7 +40982,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -41055,7 +41055,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -41128,7 +41128,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -41201,7 +41201,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -41274,7 +41274,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -41347,7 +41347,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -41420,7 +41420,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -41493,7 +41493,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -41566,7 +41566,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -41639,7 +41639,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -41712,7 +41712,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -41785,7 +41785,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -41858,7 +41858,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -41931,7 +41931,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -42004,7 +42004,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -42077,7 +42077,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -42150,7 +42150,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -42223,7 +42223,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -42296,7 +42296,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -42369,7 +42369,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -42442,7 +42442,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -42515,7 +42515,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -42588,7 +42588,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -42661,7 +42661,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -42734,7 +42734,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -42807,7 +42807,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -42880,7 +42880,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -42953,7 +42953,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -43026,7 +43026,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -43099,7 +43099,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -43172,7 +43172,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -43245,7 +43245,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -43318,7 +43318,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -43391,7 +43391,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -43464,7 +43464,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -43537,7 +43537,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -43610,7 +43610,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -43683,7 +43683,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -43756,7 +43756,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -43829,7 +43829,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -43902,7 +43902,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -43975,7 +43975,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -44048,7 +44048,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -44121,7 +44121,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -44194,7 +44194,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -44267,7 +44267,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -44340,7 +44340,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -44413,7 +44413,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -44559,7 +44559,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -44632,7 +44632,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -44705,7 +44705,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -44778,7 +44778,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -44851,7 +44851,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -44924,7 +44924,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -44997,7 +44997,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -45070,7 +45070,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -45143,7 +45143,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -45216,7 +45216,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -45289,7 +45289,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -45362,7 +45362,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -45435,7 +45435,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45508,7 +45508,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45654,7 +45654,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45800,7 +45800,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -45873,7 +45873,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -45946,7 +45946,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46019,7 +46019,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46092,7 +46092,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46165,7 +46165,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -46238,7 +46238,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -46311,7 +46311,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -46384,7 +46384,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -46530,7 +46530,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -46603,7 +46603,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -46676,7 +46676,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -46822,7 +46822,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -46895,7 +46895,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -46968,7 +46968,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -47041,7 +47041,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -47114,7 +47114,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -47187,7 +47187,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -47260,7 +47260,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -47333,7 +47333,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -47406,7 +47406,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -47479,7 +47479,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -47552,7 +47552,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -47625,7 +47625,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -47698,7 +47698,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -47771,7 +47771,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -47844,7 +47844,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -47917,7 +47917,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -47990,7 +47990,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -48136,7 +48136,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -48209,7 +48209,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -48282,7 +48282,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -48355,7 +48355,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -48428,7 +48428,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -48501,7 +48501,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -48574,7 +48574,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -48647,7 +48647,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -48720,7 +48720,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -48793,7 +48793,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -48866,7 +48866,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -48939,7 +48939,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -49012,7 +49012,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -49085,7 +49085,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -49158,7 +49158,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -49231,7 +49231,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -49304,7 +49304,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -49377,7 +49377,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -49450,7 +49450,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_134624_140/tracing_20260324_134624_140.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_134624_140\tracing_20260324_134624_140.xlsx</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -49523,7 +49523,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_140206_258/tracing_20260324_140206_258.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_140206_258\tracing_20260324_140206_258.xlsx</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -49596,7 +49596,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_142044_769/tracing_20260324_142044_769.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_142044_769\tracing_20260324_142044_769.xlsx</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -49669,7 +49669,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_143535_821/tracing_20260324_143535_821.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_143535_821\tracing_20260324_143535_821.xlsx</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -49742,7 +49742,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_144957_664/tracing_20260324_144957_664.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_144957_664\tracing_20260324_144957_664.xlsx</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -49815,7 +49815,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_150430_862/tracing_20260324_150430_862.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_150430_862\tracing_20260324_150430_862.xlsx</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -49888,7 +49888,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_151939_470/tracing_20260324_151939_470.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_151939_470\tracing_20260324_151939_470.xlsx</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -49961,7 +49961,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_153358_884/tracing_20260324_153358_884.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_153358_884\tracing_20260324_153358_884.xlsx</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -50034,7 +50034,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_154817_117/tracing_20260324_154817_117.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_154817_117\tracing_20260324_154817_117.xlsx</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -50107,7 +50107,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_161028_916/tracing_20260324_161028_916.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_161028_916\tracing_20260324_161028_916.xlsx</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -50180,7 +50180,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_162607_955/tracing_20260324_162607_955.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_162607_955\tracing_20260324_162607_955.xlsx</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -50253,7 +50253,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_164020_336/tracing_20260324_164020_336.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_164020_336\tracing_20260324_164020_336.xlsx</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -50326,7 +50326,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_165457_259/tracing_20260324_165457_259.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_165457_259\tracing_20260324_165457_259.xlsx</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -50399,7 +50399,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_171123_440/tracing_20260324_171123_440.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_171123_440\tracing_20260324_171123_440.xlsx</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -50472,7 +50472,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_172653_662/tracing_20260324_172653_662.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_172653_662\tracing_20260324_172653_662.xlsx</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -50545,7 +50545,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_174442_353/tracing_20260324_174442_353.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_174442_353\tracing_20260324_174442_353.xlsx</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -50618,7 +50618,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_180000_524/tracing_20260324_180000_524.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_180000_524\tracing_20260324_180000_524.xlsx</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -50691,7 +50691,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_181816_047/tracing_20260324_181816_047.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_181816_047\tracing_20260324_181816_047.xlsx</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -50764,7 +50764,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_183825_815/tracing_20260324_183825_815.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_183825_815\tracing_20260324_183825_815.xlsx</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -50837,7 +50837,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>/home/ivan/miso/automated-prompt-interface/out/runs/advanced_prompt_arch_comparison/20260324_185818_370/tracing_20260324_185818_370.xlsx</t>
+          <t>out\runs\gpt-4o-mini\advanced_prompt_arch_comparison\20260324_185818_370\tracing_20260324_185818_370.xlsx</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
